--- a/data/mapas/Mapa_de_Carrera_Ciencias_de_la_Educacion.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Ciencias_de_la_Educacion.xlsx
@@ -555,13 +555,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B34, "SI")</f>
+        <f>COUNTIF(B6:B41, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C34, "SI")</f>
+        <f>COUNTIF(C6:C41, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F34, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F41, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía</t>
+          <t>Pedagogía General</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B34, "SI")/24</f>
+        <f>COUNTIF(B6:B41, "SI")/32</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Didáctica General</t>
+          <t>Filosofía General</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C34, "SI")/24</f>
+        <f>COUNTIF(C6:C41, "SI")/32</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Introducción a la Disciplina</t>
+          <t>Antropología y Educación</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente I</t>
+          <t>Psicología General y del Desarrollo</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -831,10 +831,37 @@
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Sociología General</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E10" s="10">
+        <f>IF(B10="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F10" s="10">
+        <f>IF(C10="SI", "APROBADO", IF(B10="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G10" s="11">
+        <f>IF(C10="SI", "🟢 Aprobada", IF(B10="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I10" s="14" t="inlineStr">
         <is>
@@ -845,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Psicología Educacional</t>
+          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -860,7 +887,7 @@
       </c>
       <c r="D11" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E11" s="10">
@@ -884,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Sociología de la Educación</t>
+          <t>Trabajo de Campo I</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -899,7 +926,7 @@
       </c>
       <c r="D12" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E12" s="10">
@@ -921,37 +948,10 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Sujetos de la Educación</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E13" s="10">
-        <f>IF(B13="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F13" s="10">
-        <f>IF(C13="SI", "APROBADO", IF(B13="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G13" s="11">
-        <f>IF(C13="SI", "🟢 Aprobada", IF(B13="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente II</t>
+          <t>Didáctica General</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -999,10 +999,37 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Historia de la Educación Argentina y Latinoamericana</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E15" s="10">
+        <f>IF(B15="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F15" s="10">
+        <f>IF(C15="SI", "APROBADO", IF(B15="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G15" s="11">
+        <f>IF(C15="SI", "🟢 Aprobada", IF(B15="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -1013,7 +1040,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Historia Social de la Educación</t>
+          <t>Sociología de la Educación</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1028,7 +1055,7 @@
       </c>
       <c r="D16" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E16" s="10">
@@ -1047,7 +1074,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Residencia I</t>
+          <t>Psicología de la Educación</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1062,7 +1089,7 @@
       </c>
       <c r="D17" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E17" s="10">
@@ -1081,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Espacio de Definición Institucional</t>
+          <t>Instituciones Educativas y Análisis Organizacional</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1096,7 +1123,7 @@
       </c>
       <c r="D18" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E18" s="10">
@@ -1115,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente III</t>
+          <t>Filosofía de la Educación</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1130,7 +1157,7 @@
       </c>
       <c r="D19" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E19" s="10">
@@ -1146,17 +1173,44 @@
         <v/>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Estado, Sociedad y Derechos Humanos</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E20" s="10">
+        <f>IF(B20="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F20" s="10">
+        <f>IF(C20="SI", "APROBADO", IF(B20="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G20" s="11">
+        <f>IF(C20="SI", "🟢 Aprobada", IF(B20="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Residencia II / Taller de Cierre</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1171,7 +1225,7 @@
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E21" s="10">
@@ -1187,44 +1241,17 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>Ética y Trabajo Docente</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C22" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D22" s="10" t="inlineStr">
-        <is>
-          <t>4° Año</t>
-        </is>
-      </c>
-      <c r="E22" s="10">
-        <f>IF(B22="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F22" s="10">
-        <f>IF(C22="SI", "APROBADO", IF(B22="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G22" s="11">
-        <f>IF(C22="SI", "🟢 Aprobada", IF(B22="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Investigación Educativa</t>
+          <t>Teoría y Diseño Curricular</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1239,7 +1266,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E23" s="10">
@@ -1258,7 +1285,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Práctica Docente IV</t>
+          <t>Política y Legislación Educativa</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1273,7 +1300,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E24" s="10">
@@ -1289,17 +1316,44 @@
         <v/>
       </c>
     </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>📌 5° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
-        </is>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Metodología de la Investigación Educativa I (Cualitativa)</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E25" s="10">
+        <f>IF(B25="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F25" s="10">
+        <f>IF(C25="SI", "APROBADO", IF(B25="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G25" s="11">
+        <f>IF(C25="SI", "🟢 Aprobada", IF(B25="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Especialización Superior I</t>
+          <t>Didáctica de Nivel Inicial, Primario y Secundario</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1314,7 +1368,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E26" s="10">
@@ -1333,7 +1387,7 @@
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>Taller de Investigación Aplicada</t>
+          <t>Historia Social de la Educación</t>
         </is>
       </c>
       <c r="B27" s="9" t="inlineStr">
@@ -1348,7 +1402,7 @@
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E27" s="10">
@@ -1367,7 +1421,7 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de Nivel Superior</t>
+          <t>Problemas Didácticos Contemporáneos</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1382,7 +1436,7 @@
       </c>
       <c r="D28" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E28" s="10">
@@ -1401,7 +1455,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Práctica de Nivel Superior I</t>
+          <t>Construcción de la Práctica Docente I</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1416,7 +1470,7 @@
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>5° Año (Nivel Superior / Tramo Superior)</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E29" s="10">
@@ -1435,14 +1489,14 @@
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>📌 6° AÑO (NIVEL SUPERIOR / TRAMO SUPERIOR)</t>
+          <t>📌 4° AÑO</t>
         </is>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Especialización Superior II</t>
+          <t>Planeamiento y Gestión Educativa</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1457,7 +1511,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E31" s="10">
@@ -1476,7 +1530,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Tesis / Trabajo Final de Licenciatura</t>
+          <t>Metodología de la Investigación Educativa II (Cuantitativa y Mixta)</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1491,7 +1545,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1510,7 +1564,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Práctica de Nivel Superior II</t>
+          <t>Evaluación de Proyectos Educativos</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1525,7 +1579,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1544,7 +1598,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Acreditación de Residencia Superior</t>
+          <t>Educación No Formal y Pedagogía Social</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1559,7 +1613,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>6° Año (Nivel Superior / Tramo Superior)</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E34" s="10">
@@ -1575,27 +1629,237 @@
         <v/>
       </c>
     </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>Educación Sexual Integral (ESI)</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E35" s="10">
+        <f>IF(B35="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F35" s="10">
+        <f>IF(C35="SI", "APROBADO", IF(B35="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G35" s="11">
+        <f>IF(C35="SI", "🟢 Aprobada", IF(B35="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>Ética y Trabajo Docente</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E36" s="10">
+        <f>IF(B36="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F36" s="10">
+        <f>IF(C36="SI", "APROBADO", IF(B36="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G36" s="11">
+        <f>IF(C36="SI", "🟢 Aprobada", IF(B36="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Residencia y Construcción de la Práctica Docente II</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D37" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E37" s="10">
+        <f>IF(B37="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F37" s="10">
+        <f>IF(C37="SI", "APROBADO", IF(B37="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G37" s="11">
+        <f>IF(C37="SI", "🟢 Aprobada", IF(B37="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Seminario de Políticas Públicas Educativas</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E39" s="10">
+        <f>IF(B39="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F39" s="10">
+        <f>IF(C39="SI", "APROBADO", IF(B39="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G39" s="11">
+        <f>IF(C39="SI", "🟢 Aprobada", IF(B39="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Seminario de Educación Superior y Universitaria</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E40" s="10">
+        <f>IF(B40="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F40" s="10">
+        <f>IF(C40="SI", "APROBADO", IF(B40="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G40" s="11">
+        <f>IF(C40="SI", "🟢 Aprobada", IF(B40="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Taller de Trabajo Final / Tesis de Licenciatura</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E41" s="10">
+        <f>IF(B41="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F41" s="10">
+        <f>IF(C41="SI", "APROBADO", IF(B41="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G41" s="11">
+        <f>IF(C41="SI", "🟢 Aprobada", IF(B41="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="16">
-    <mergeCell ref="I14:J14"/>
+  <mergeCells count="15">
+    <mergeCell ref="A13:G13"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="A22:G22"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A20:G20"/>
     <mergeCell ref="A30:G30"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="I14:J14"/>
     <mergeCell ref="I9:J9"/>
-    <mergeCell ref="A10:G10"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B11 B12 B13 B14 B16 B17 B18 B19 B21 B22 B23 B24 B26 B27 B28 B29 B31 B32 B33 B34 C6 C7 C8 C9 C11 C12 C13 C14 C16 C17 C18 C19 C21 C22 C23 C24 C26 C27 C28 C29 C31 C32 C33 C34" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B14 B15 B16 B17 B18 B19 B20 B21 B23 B24 B25 B26 B27 B28 B29 B31 B32 B33 B34 B35 B36 B37 B39 B40 B41 C6 C7 C8 C9 C10 C11 C12 C14 C15 C16 C17 C18 C19 C20 C21 C23 C24 C25 C26 C27 C28 C29 C31 C32 C33 C34 C35 C36 C37 C39 C40 C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>

--- a/data/mapas/Mapa_de_Carrera_Ciencias_de_la_Educacion.xlsx
+++ b/data/mapas/Mapa_de_Carrera_Ciencias_de_la_Educacion.xlsx
@@ -555,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K41"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="54" customWidth="1" min="1" max="1"/>
@@ -595,7 +595,7 @@
         </is>
       </c>
       <c r="J2" s="5" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
@@ -605,7 +605,7 @@
         </is>
       </c>
       <c r="J3" s="5">
-        <f>COUNTIF(B6:B41, "SI")</f>
+        <f>COUNTIF(B6:B55, "SI")</f>
         <v/>
       </c>
     </row>
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="J4" s="5">
-        <f>COUNTIF(C6:C41, "SI")</f>
+        <f>COUNTIF(C6:C55, "SI")</f>
         <v/>
       </c>
     </row>
@@ -667,14 +667,14 @@
         </is>
       </c>
       <c r="J5" s="5">
-        <f>COUNTIF(F6:F41, "ADEUDA FINAL")</f>
+        <f>COUNTIF(F6:F55, "ADEUDA FINAL")</f>
         <v/>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Pedagogía General</t>
+          <t>Pedagogía</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -710,14 +710,14 @@
         </is>
       </c>
       <c r="J6" s="12">
-        <f>COUNTIF(B6:B41, "SI")/32</f>
+        <f>COUNTIF(B6:B55, "SI")/45</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Filosofía General</t>
+          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="J7" s="12">
-        <f>COUNTIF(C6:C41, "SI")/32</f>
+        <f>COUNTIF(C6:C55, "SI")/45</f>
         <v/>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Antropología y Educación</t>
+          <t>Antropología social y cultural</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -794,7 +794,7 @@
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Psicología General y del Desarrollo</t>
+          <t>Psicología General</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Sociología General</t>
+          <t>Bases biologicas de la subjetividad</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -872,7 +872,7 @@
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Lectura, Escritura y Oralidad I (LEO 1)</t>
+          <t>Filosofía</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -911,7 +911,7 @@
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo I</t>
+          <t>Estudios culturales y educación</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
@@ -948,10 +948,37 @@
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>📌 2° AÑO</t>
-        </is>
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Trabajo de Campo I</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>1° Año</t>
+        </is>
+      </c>
+      <c r="E13" s="10">
+        <f>IF(B13="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F13" s="10">
+        <f>IF(C13="SI", "APROBADO", IF(B13="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G13" s="11">
+        <f>IF(C13="SI", "🟢 Aprobada", IF(B13="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -962,7 +989,7 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Didáctica General</t>
+          <t>Esi</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
@@ -977,7 +1004,7 @@
       </c>
       <c r="D14" s="10" t="inlineStr">
         <is>
-          <t>2° Año</t>
+          <t>1° Año</t>
         </is>
       </c>
       <c r="E14" s="10">
@@ -999,37 +1026,10 @@
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Historia de la Educación Argentina y Latinoamericana</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C15" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D15" s="10" t="inlineStr">
-        <is>
-          <t>2° Año</t>
-        </is>
-      </c>
-      <c r="E15" s="10">
-        <f>IF(B15="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F15" s="10">
-        <f>IF(C15="SI", "APROBADO", IF(B15="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G15" s="11">
-        <f>IF(C15="SI", "🟢 Aprobada", IF(B15="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+      <c r="A15" s="7" t="inlineStr">
+        <is>
+          <t>📌 2° AÑO</t>
+        </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
     <row r="16" ht="20" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Sociología de la Educación</t>
+          <t>Psicología ciclos vitales</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
@@ -1074,7 +1074,7 @@
     <row r="17" ht="20" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Psicología de la Educación</t>
+          <t>Lectura, Escritura y Oralidad II (LEO 2)</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
@@ -1108,7 +1108,7 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Instituciones Educativas y Análisis Organizacional</t>
+          <t>Didáctica general</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
@@ -1142,7 +1142,7 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Filosofía de la Educación</t>
+          <t>Sociología de la educación</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
@@ -1176,7 +1176,7 @@
     <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Estado, Sociedad y Derechos Humanos</t>
+          <t>Filosofía de la educación</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
@@ -1210,7 +1210,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Trabajo de Campo II</t>
+          <t>Instituciones educativas</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
@@ -1241,17 +1241,44 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>📌 3° AÑO</t>
-        </is>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Psicologia de la educación</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>2° Año</t>
+        </is>
+      </c>
+      <c r="E22" s="10">
+        <f>IF(B22="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F22" s="10">
+        <f>IF(C22="SI", "APROBADO", IF(B22="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G22" s="11">
+        <f>IF(C22="SI", "🟢 Aprobada", IF(B22="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Teoría y Diseño Curricular</t>
+          <t>Estado, sociedad y DDHH</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
@@ -1266,7 +1293,7 @@
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E23" s="10">
@@ -1285,7 +1312,7 @@
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>Política y Legislación Educativa</t>
+          <t>Nuevas tecnologias</t>
         </is>
       </c>
       <c r="B24" s="9" t="inlineStr">
@@ -1300,7 +1327,7 @@
       </c>
       <c r="D24" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E24" s="10">
@@ -1319,7 +1346,7 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>Metodología de la Investigación Educativa I (Cualitativa)</t>
+          <t>Trabajo de Campo II</t>
         </is>
       </c>
       <c r="B25" s="9" t="inlineStr">
@@ -1334,7 +1361,7 @@
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E25" s="10">
@@ -1353,7 +1380,7 @@
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>Didáctica de Nivel Inicial, Primario y Secundario</t>
+          <t>Psicología social y analisis de las organizaciones educativas</t>
         </is>
       </c>
       <c r="B26" s="9" t="inlineStr">
@@ -1368,7 +1395,7 @@
       </c>
       <c r="D26" s="10" t="inlineStr">
         <is>
-          <t>3° Año</t>
+          <t>2° Año</t>
         </is>
       </c>
       <c r="E26" s="10">
@@ -1384,44 +1411,17 @@
         <v/>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Historia Social de la Educación</t>
-        </is>
-      </c>
-      <c r="B27" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D27" s="10" t="inlineStr">
-        <is>
-          <t>3° Año</t>
-        </is>
-      </c>
-      <c r="E27" s="10">
-        <f>IF(B27="SI", "REGULAR", "PENDIENTE")</f>
-        <v/>
-      </c>
-      <c r="F27" s="10">
-        <f>IF(C27="SI", "APROBADO", IF(B27="SI", "ADEUDA FINAL", "ADEUDA"))</f>
-        <v/>
-      </c>
-      <c r="G27" s="11">
-        <f>IF(C27="SI", "🟢 Aprobada", IF(B27="SI", "🟡 Regular", "🟣 Pendiente"))</f>
-        <v/>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>📌 3° AÑO</t>
+        </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>Problemas Didácticos Contemporáneos</t>
+          <t>Historia social de la educación</t>
         </is>
       </c>
       <c r="B28" s="9" t="inlineStr">
@@ -1455,7 +1455,7 @@
     <row r="29" ht="20" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>Construcción de la Práctica Docente I</t>
+          <t>Problemas didacticos 1</t>
         </is>
       </c>
       <c r="B29" s="9" t="inlineStr">
@@ -1486,17 +1486,44 @@
         <v/>
       </c>
     </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>📌 4° AÑO</t>
-        </is>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>Educación no formal e informal</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>3° Año</t>
+        </is>
+      </c>
+      <c r="E30" s="10">
+        <f>IF(B30="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F30" s="10">
+        <f>IF(C30="SI", "APROBADO", IF(B30="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G30" s="11">
+        <f>IF(C30="SI", "🟢 Aprobada", IF(B30="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>Planeamiento y Gestión Educativa</t>
+          <t>Trabajo de Campo III</t>
         </is>
       </c>
       <c r="B31" s="9" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="D31" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E31" s="10">
@@ -1530,7 +1557,7 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>Metodología de la Investigación Educativa II (Cuantitativa y Mixta)</t>
+          <t>Curriculum</t>
         </is>
       </c>
       <c r="B32" s="9" t="inlineStr">
@@ -1545,7 +1572,7 @@
       </c>
       <c r="D32" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E32" s="10">
@@ -1564,7 +1591,7 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>Evaluación de Proyectos Educativos</t>
+          <t>Evaluación</t>
         </is>
       </c>
       <c r="B33" s="9" t="inlineStr">
@@ -1579,7 +1606,7 @@
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E33" s="10">
@@ -1598,7 +1625,7 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>Educación No Formal y Pedagogía Social</t>
+          <t>Trabajo docente</t>
         </is>
       </c>
       <c r="B34" s="9" t="inlineStr">
@@ -1613,7 +1640,7 @@
       </c>
       <c r="D34" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E34" s="10">
@@ -1632,7 +1659,7 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>Educación Sexual Integral (ESI)</t>
+          <t>Lengua Extranjera</t>
         </is>
       </c>
       <c r="B35" s="9" t="inlineStr">
@@ -1647,7 +1674,7 @@
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E35" s="10">
@@ -1666,7 +1693,7 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>Ética y Trabajo Docente</t>
+          <t>Epistemologia de las ciencias sociales</t>
         </is>
       </c>
       <c r="B36" s="9" t="inlineStr">
@@ -1681,7 +1708,7 @@
       </c>
       <c r="D36" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E36" s="10">
@@ -1700,7 +1727,7 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t>Residencia y Construcción de la Práctica Docente II</t>
+          <t>Sistema y política educativa</t>
         </is>
       </c>
       <c r="B37" s="9" t="inlineStr">
@@ -1715,7 +1742,7 @@
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>4° Año</t>
+          <t>3° Año</t>
         </is>
       </c>
       <c r="E37" s="10">
@@ -1734,14 +1761,14 @@
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
+          <t>📌 4° AÑO</t>
         </is>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Políticas Públicas Educativas</t>
+          <t>Metodologia de la investigación educativa</t>
         </is>
       </c>
       <c r="B39" s="9" t="inlineStr">
@@ -1756,7 +1783,7 @@
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E39" s="10">
@@ -1775,7 +1802,7 @@
     <row r="40" ht="20" customHeight="1">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t>Seminario de Educación Superior y Universitaria</t>
+          <t>Estadistica socioeducativa</t>
         </is>
       </c>
       <c r="B40" s="9" t="inlineStr">
@@ -1790,7 +1817,7 @@
       </c>
       <c r="D40" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E40" s="10">
@@ -1809,7 +1836,7 @@
     <row r="41" ht="20" customHeight="1">
       <c r="A41" s="8" t="inlineStr">
         <is>
-          <t>Taller de Trabajo Final / Tesis de Licenciatura</t>
+          <t>Legislación educativa</t>
         </is>
       </c>
       <c r="B41" s="9" t="inlineStr">
@@ -1824,7 +1851,7 @@
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Tramo Superior / Seminarios</t>
+          <t>4° Año</t>
         </is>
       </c>
       <c r="E41" s="10">
@@ -1840,26 +1867,449 @@
         <v/>
       </c>
     </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Construcción de la practica docente 1</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E42" s="10">
+        <f>IF(B42="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F42" s="10">
+        <f>IF(C42="SI", "APROBADO", IF(B42="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G42" s="11">
+        <f>IF(C42="SI", "🟢 Aprobada", IF(B42="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Políticas epistematicas</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E43" s="10">
+        <f>IF(B43="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F43" s="10">
+        <f>IF(C43="SI", "APROBADO", IF(B43="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G43" s="11">
+        <f>IF(C43="SI", "🟢 Aprobada", IF(B43="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Historia de la educación Argentina</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E44" s="10">
+        <f>IF(B44="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F44" s="10">
+        <f>IF(C44="SI", "APROBADO", IF(B44="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G44" s="11">
+        <f>IF(C44="SI", "🟢 Aprobada", IF(B44="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>Autoridad pedagógica</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E45" s="10">
+        <f>IF(B45="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F45" s="10">
+        <f>IF(C45="SI", "APROBADO", IF(B45="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G45" s="11">
+        <f>IF(C45="SI", "🟢 Aprobada", IF(B45="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="8" t="inlineStr">
+        <is>
+          <t>Problemas didacticos 2</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E46" s="10">
+        <f>IF(B46="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F46" s="10">
+        <f>IF(C46="SI", "APROBADO", IF(B46="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G46" s="11">
+        <f>IF(C46="SI", "🟢 Aprobada", IF(B46="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="8" t="inlineStr">
+        <is>
+          <t>Dimensión etica del trabajo docente</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E47" s="10">
+        <f>IF(B47="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F47" s="10">
+        <f>IF(C47="SI", "APROBADO", IF(B47="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G47" s="11">
+        <f>IF(C47="SI", "🟢 Aprobada", IF(B47="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Pedagogía social</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>4° Año</t>
+        </is>
+      </c>
+      <c r="E48" s="10">
+        <f>IF(B48="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F48" s="10">
+        <f>IF(C48="SI", "APROBADO", IF(B48="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G48" s="11">
+        <f>IF(C48="SI", "🟢 Aprobada", IF(B48="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" ht="22" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>📌 5° AÑO</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>Configuración dinamica de roles profesionales</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E50" s="10">
+        <f>IF(B50="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F50" s="10">
+        <f>IF(C50="SI", "APROBADO", IF(B50="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G50" s="11">
+        <f>IF(C50="SI", "🟢 Aprobada", IF(B50="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Practica de la investigación educativa</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>5° Año</t>
+        </is>
+      </c>
+      <c r="E51" s="10">
+        <f>IF(B51="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F51" s="10">
+        <f>IF(C51="SI", "APROBADO", IF(B51="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G51" s="11">
+        <f>IF(C51="SI", "🟢 Aprobada", IF(B51="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>📌 TRAMO SUPERIOR / SEMINARIOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
+        <is>
+          <t>Construcción de la practica docente 2</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E53" s="10">
+        <f>IF(B53="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F53" s="10">
+        <f>IF(C53="SI", "APROBADO", IF(B53="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G53" s="11">
+        <f>IF(C53="SI", "🟢 Aprobada", IF(B53="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>Ateneo de politicas publicas</t>
+        </is>
+      </c>
+      <c r="B54" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D54" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E54" s="10">
+        <f>IF(B54="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F54" s="10">
+        <f>IF(C54="SI", "APROBADO", IF(B54="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G54" s="11">
+        <f>IF(C54="SI", "🟢 Aprobada", IF(B54="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="8" t="inlineStr">
+        <is>
+          <t>Experiencias educativas en contexto</t>
+        </is>
+      </c>
+      <c r="B55" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="C55" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>Tramo Superior / Seminarios</t>
+        </is>
+      </c>
+      <c r="E55" s="10">
+        <f>IF(B55="SI", "REGULAR", "PENDIENTE")</f>
+        <v/>
+      </c>
+      <c r="F55" s="10">
+        <f>IF(C55="SI", "APROBADO", IF(B55="SI", "ADEUDA FINAL", "ADEUDA"))</f>
+        <v/>
+      </c>
+      <c r="G55" s="11">
+        <f>IF(C55="SI", "🟢 Aprobada", IF(B55="SI", "🟡 Regular", "🟣 Pendiente"))</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A13:G13"/>
+  <mergeCells count="16">
+    <mergeCell ref="I14:J14"/>
     <mergeCell ref="I12:J12"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A27:G27"/>
     <mergeCell ref="I15:J15"/>
     <mergeCell ref="I10:J10"/>
-    <mergeCell ref="A22:G22"/>
     <mergeCell ref="I1:K1"/>
     <mergeCell ref="I11:J11"/>
-    <mergeCell ref="A30:G30"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A52:G52"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="A49:G49"/>
     <mergeCell ref="I9:J9"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B14 B15 B16 B17 B18 B19 B20 B21 B23 B24 B25 B26 B27 B28 B29 B31 B32 B33 B34 B35 B36 B37 B39 B40 B41 C6 C7 C8 C9 C10 C11 C12 C14 C15 C16 C17 C18 C19 C20 C21 C23 C24 C25 C26 C27 C28 C29 C31 C32 C33 C34 C35 C36 C37 C39 C40 C41" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
+    <dataValidation sqref="B6 B7 B8 B9 B10 B11 B12 B13 B14 B16 B17 B18 B19 B20 B21 B22 B23 B24 B25 B26 B28 B29 B30 B31 B32 B33 B34 B35 B36 B37 B39 B40 B41 B42 B43 B44 B45 B46 B47 B48 B50 B51 B53 B54 B55 C6 C7 C8 C9 C10 C11 C12 C13 C14 C16 C17 C18 C19 C20 C21 C22 C23 C24 C25 C26 C28 C29 C30 C31 C32 C33 C34 C35 C36 C37 C39 C40 C41 C42 C43 C44 C45 C46 C47 C48 C50 C51 C53 C54 C55" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Opción inválida" error="Por favor, elegí 'SI' o 'NO' de la lista desplegable." type="list">
       <formula1>"SI,NO"</formula1>
     </dataValidation>
   </dataValidations>
